--- a/projects/blog-growth/블로그-KPI-트래커.xlsx
+++ b/projects/blog-growth/블로그-KPI-트래커.xlsx
@@ -13,6 +13,7 @@
     <sheet name="글별성과" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="키워드백로그" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="콘텐츠캘린더" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="근거데이터" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -118,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -154,6 +155,9 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -709,13 +713,13 @@
       </c>
       <c r="B4" s="8" t="n"/>
       <c r="C4" s="9" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="D4" s="9" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="E4" s="9" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
@@ -790,13 +794,13 @@
       </c>
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>2</v>
-      </c>
       <c r="E7" s="9" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
@@ -817,13 +821,13 @@
       </c>
       <c r="B8" s="8" t="n"/>
       <c r="C8" s="9" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
@@ -844,13 +848,13 @@
       </c>
       <c r="B9" s="10" t="n"/>
       <c r="C9" s="11" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D9" s="11" t="n">
         <v>0.02</v>
       </c>
-      <c r="D9" s="11" t="n">
-        <v>0.03</v>
-      </c>
       <c r="E9" s="11" t="n">
-        <v>0.035</v>
+        <v>0.025</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
@@ -893,7 +897,7 @@
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>목표 배수 가정: AI 브리핑 이후 네이버 검색 유입 감소 추세(2026 보도 기준)를 감안한 보수적 추정치. 4주차 점검 후 조정하세요.</t>
+          <t>목표 배수 근거(2차 개정): 네이버 AI 브리핑 적용 20%→40% 확대 예정(검색 클릭 감소), 구글 신규 페이지 1년 내 Top10 진입 1.74%(Ahrefs 2025), AI 요약 시 1위 CTR 9.7%(AWR). 상세는 '근거데이터' 시트. 4주차 점검 후 조정하세요.</t>
         </is>
       </c>
     </row>
@@ -8215,17 +8219,31 @@
       </c>
       <c r="J16" s="9" t="inlineStr">
         <is>
-          <t>12월 초 정기국회</t>
+          <t>법정기한 12/2</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="n"/>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>파킹형 ETF 비교</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>C.배당ETF</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>둘 다</t>
+        </is>
+      </c>
       <c r="D17" s="15" t="n"/>
       <c r="E17" s="8" t="n"/>
-      <c r="F17" s="9" t="n"/>
+      <c r="F17" s="9" t="n">
+        <v>1.5</v>
+      </c>
       <c r="G17" s="7">
         <f>IF(D17="","",IF(D17&lt;300,1,IF(D17&lt;1000,2,IF(D17&lt;5000,4,IF(D17&lt;30000,5,3)))))</f>
         <v/>
@@ -8234,16 +8252,38 @@
         <f>IF(OR(G17="",E17="",E17=0),"",ROUND(G17*F17/E17,2))</f>
         <v/>
       </c>
-      <c r="I17" s="9" t="n"/>
-      <c r="J17" s="9" t="n"/>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>대기</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>9월 중순 한 주 1.8조 유입</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="n"/>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="9" t="n"/>
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>잠자는 ISA 활용법</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>A.ISA</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>네이버</t>
+        </is>
+      </c>
       <c r="D18" s="15" t="n"/>
       <c r="E18" s="8" t="n"/>
-      <c r="F18" s="9" t="n"/>
+      <c r="F18" s="9" t="n">
+        <v>1.3</v>
+      </c>
       <c r="G18" s="7">
         <f>IF(D18="","",IF(D18&lt;300,1,IF(D18&lt;1000,2,IF(D18&lt;5000,4,IF(D18&lt;30000,5,3)))))</f>
         <v/>
@@ -8252,16 +8292,38 @@
         <f>IF(OR(G18="",E18="",E18=0),"",ROUND(G18*F18/E18,2))</f>
         <v/>
       </c>
-      <c r="I18" s="9" t="n"/>
-      <c r="J18" s="9" t="n"/>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>대기</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>ISA 48.5%가 잔액 1만원 이하</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="n"/>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>배당기준일 변경</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>C.배당ETF</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>티스토리</t>
+        </is>
+      </c>
       <c r="D19" s="15" t="n"/>
       <c r="E19" s="8" t="n"/>
-      <c r="F19" s="9" t="n"/>
+      <c r="F19" s="9" t="n">
+        <v>1.2</v>
+      </c>
       <c r="G19" s="7">
         <f>IF(D19="","",IF(D19&lt;300,1,IF(D19&lt;1000,2,IF(D19&lt;5000,4,IF(D19&lt;30000,5,3)))))</f>
         <v/>
@@ -8270,16 +8332,38 @@
         <f>IF(OR(G19="",E19="",E19=0),"",ROUND(G19*F19/E19,2))</f>
         <v/>
       </c>
-      <c r="I19" s="9" t="n"/>
-      <c r="J19" s="9" t="n"/>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>대기</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>KOSPI200 중 98개사 기준일 이동</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="n"/>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>TIGER KODEX S&amp;P500 비교</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>D.테마ETF</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>티스토리</t>
+        </is>
+      </c>
       <c r="D20" s="15" t="n"/>
       <c r="E20" s="8" t="n"/>
-      <c r="F20" s="9" t="n"/>
+      <c r="F20" s="9" t="n">
+        <v>1.2</v>
+      </c>
       <c r="G20" s="7">
         <f>IF(D20="","",IF(D20&lt;300,1,IF(D20&lt;1000,2,IF(D20&lt;5000,4,IF(D20&lt;30000,5,3)))))</f>
         <v/>
@@ -8288,8 +8372,16 @@
         <f>IF(OR(G20="",E20="",E20=0),"",ROUND(G20*F20/E20,2))</f>
         <v/>
       </c>
-      <c r="I20" s="9" t="n"/>
-      <c r="J20" s="9" t="n"/>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>대기</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>하반기 개인 순매수 1위</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="n"/>
@@ -9850,18 +9942,18 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>기존 상위 10개 글 리라이팅</t>
+          <t>기존 상위 글 리라이팅 시작</t>
         </is>
       </c>
       <c r="D3" s="7" t="n">
         <v>3</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>ISA 허브 글 (티스토리)</t>
+          <t>파킹형 ETF 비교 (금통위 10/22 전) / ISA 허브(T)</t>
         </is>
       </c>
       <c r="G3" s="8" t="n"/>
@@ -9880,18 +9972,18 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>클러스터 A 완성</t>
+          <t>클러스터 B 앞당김 (연금 입금 30%가 11~12월)</t>
         </is>
       </c>
       <c r="D4" s="7" t="n">
         <v>3</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>생산적금융 ISA vs 일반 ISA / ISA에 담을 ETF</t>
+          <t>연금저축·IRP ETF 허브, 세액공제 계산</t>
         </is>
       </c>
       <c r="G4" s="8" t="n"/>
@@ -9914,14 +10006,14 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>고배당 ETF 비교</t>
+          <t>분기 분배 기준일 안내, 금통위 결과</t>
         </is>
       </c>
       <c r="G5" s="8" t="n"/>
@@ -9940,18 +10032,18 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>클러스터 C</t>
+          <t>연말정산 미리보기 개시 → 연금 글 업데이트</t>
         </is>
       </c>
       <c r="D6" s="7" t="n">
         <v>3</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>월배당·커버드콜 ETF</t>
+          <t>연말 절세 체크리스트, ISA→연금 이체</t>
         </is>
       </c>
       <c r="G6" s="8" t="n"/>
@@ -9970,18 +10062,18 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>클러스터 B 시작 (연말 수요 선점)</t>
+          <t>클러스터 A 완성</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>연금저축·IRP ETF 허브</t>
+          <t>생산적금융 ISA vs 일반 ISA, 잠자는 ISA 활용법</t>
         </is>
       </c>
       <c r="G7" s="8" t="n"/>
@@ -10000,18 +10092,18 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>클러스터 B</t>
+          <t>클러스터 C (방어형)</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
         <v>3</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>세액공제 계산 / ISA→연금 이체</t>
+          <t>커버드콜 분배율과 원금 훼손 위험</t>
         </is>
       </c>
       <c r="G8" s="8" t="n"/>
@@ -10030,18 +10122,18 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>2차 점검: 게재순위 8~20위 보강</t>
+          <t>2차 점검: 게재순위 8~20위 보강, 세법 속보 초안</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>연말 절세 체크리스트</t>
+          <t>금통위(11/26) 결과, 미국지수 ETF 비교</t>
         </is>
       </c>
       <c r="G9" s="8" t="n"/>
@@ -10060,18 +10152,18 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>정기국회 세법 처리 속보 + ISA 글 업데이트</t>
+          <t>세법 처리(기한 12/2) 당일 속보 + ISA 글 업데이트</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>세제개편안 확정 정리</t>
+          <t>생산적금융 ISA 확정 여부</t>
         </is>
       </c>
       <c r="G10" s="8" t="n"/>
@@ -10090,18 +10182,18 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>클러스터 D</t>
+          <t>배당기준일 변경 해설</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>신규 상장 ETF 월간 정리</t>
+          <t>배당기준일이 바뀌었다</t>
         </is>
       </c>
       <c r="G11" s="8" t="n"/>
@@ -10120,18 +10212,18 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>12월 마감 절세, 배당 기준일</t>
+          <t>12월 마감 막판 글</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
         <v>3</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>12/31 전에 할 일 / 배당 기준일</t>
+          <t>IRP 입금 마감 시간</t>
         </is>
       </c>
       <c r="G12" s="8" t="n"/>
@@ -10154,14 +10246,14 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>연말정산 대비 글 준비</t>
+          <t>생산적금융 ISA 가입, 연말정산 간소화 준비</t>
         </is>
       </c>
       <c r="G13" s="8" t="n"/>
@@ -10197,4 +10289,922 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>근거 데이터 요약 (상세·출처 링크: docs/블로그-근거데이터.md). 웹 검색 결과 기준, 원문 미열람 → 인용 전 원문 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>분야</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>지표</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>기준일</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>신뢰도</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>전략에 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>ETF 시장</t>
+        </is>
+      </c>
+      <c r="B4" s="33" t="inlineStr">
+        <is>
+          <t>국내 ETF 순자산</t>
+        </is>
+      </c>
+      <c r="C4" s="33" t="inlineStr">
+        <is>
+          <t>533조(고점) → 447조</t>
+        </is>
+      </c>
+      <c r="D4" s="33" t="inlineStr">
+        <is>
+          <t>2026-06-22 / 09-17</t>
+        </is>
+      </c>
+      <c r="E4" s="33" t="inlineStr">
+        <is>
+          <t>국민일보, 샛경제</t>
+        </is>
+      </c>
+      <c r="F4" s="33" t="inlineStr">
+        <is>
+          <t>교차확인</t>
+        </is>
+      </c>
+      <c r="G4" s="33" t="inlineStr">
+        <is>
+          <t>방어형·연금형 주제로 이동</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="33" t="inlineStr">
+        <is>
+          <t>ETF 시장</t>
+        </is>
+      </c>
+      <c r="B5" s="33" t="inlineStr">
+        <is>
+          <t>개인 연속 순매수</t>
+        </is>
+      </c>
+      <c r="C5" s="33" t="inlineStr">
+        <is>
+          <t>32개월, 누적 128조</t>
+        </is>
+      </c>
+      <c r="D5" s="33" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="E5" s="33" t="inlineStr">
+        <is>
+          <t>이데일리</t>
+        </is>
+      </c>
+      <c r="F5" s="33" t="inlineStr">
+        <is>
+          <t>교차확인</t>
+        </is>
+      </c>
+      <c r="G5" s="33" t="inlineStr">
+        <is>
+          <t>수요 지속</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="33" t="inlineStr">
+        <is>
+          <t>ETF 시장</t>
+        </is>
+      </c>
+      <c r="B6" s="33" t="inlineStr">
+        <is>
+          <t>하반기 개인 순매수 1위</t>
+        </is>
+      </c>
+      <c r="C6" s="33" t="inlineStr">
+        <is>
+          <t>TIGER 미국S&amp;P500 1.46조</t>
+        </is>
+      </c>
+      <c r="D6" s="33" t="inlineStr">
+        <is>
+          <t>2026-07-01~09-14</t>
+        </is>
+      </c>
+      <c r="E6" s="33" t="inlineStr">
+        <is>
+          <t>한국경제, 헤럴드경제</t>
+        </is>
+      </c>
+      <c r="F6" s="33" t="inlineStr">
+        <is>
+          <t>교차확인</t>
+        </is>
+      </c>
+      <c r="G6" s="33" t="inlineStr">
+        <is>
+          <t>미국지수 비교 글</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>ETF 시장</t>
+        </is>
+      </c>
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>파킹형 ETF 주간 유입</t>
+        </is>
+      </c>
+      <c r="C7" s="33" t="inlineStr">
+        <is>
+          <t>1.8조 (3종 합계)</t>
+        </is>
+      </c>
+      <c r="D7" s="33" t="inlineStr">
+        <is>
+          <t>2026-09 중순</t>
+        </is>
+      </c>
+      <c r="E7" s="33" t="inlineStr">
+        <is>
+          <t>파이낸셜뉴스, 머니투데이</t>
+        </is>
+      </c>
+      <c r="F7" s="33" t="inlineStr">
+        <is>
+          <t>교차확인</t>
+        </is>
+      </c>
+      <c r="G7" s="33" t="inlineStr">
+        <is>
+          <t>2주차 파킹형 글</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>ETF 시장</t>
+        </is>
+      </c>
+      <c r="B8" s="33" t="inlineStr">
+        <is>
+          <t>커버드콜 ETF 순자산</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>15.1조 → 27.6조</t>
+        </is>
+      </c>
+      <c r="D8" s="33" t="inlineStr">
+        <is>
+          <t>2026-01 → 08-26</t>
+        </is>
+      </c>
+      <c r="E8" s="33" t="inlineStr">
+        <is>
+          <t>헤럴드경제</t>
+        </is>
+      </c>
+      <c r="F8" s="33" t="inlineStr">
+        <is>
+          <t>교차확인</t>
+        </is>
+      </c>
+      <c r="G8" s="33" t="inlineStr">
+        <is>
+          <t>클러스터 C</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>연금·ISA</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>퇴직연금 ETF 투자액</t>
+        </is>
+      </c>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>21조 → 48.7조 → 약 60조</t>
+        </is>
+      </c>
+      <c r="D9" s="33" t="inlineStr">
+        <is>
+          <t>2024 → 2025 → 2026 2Q</t>
+        </is>
+      </c>
+      <c r="E9" s="33" t="inlineStr">
+        <is>
+          <t>비즈워치, 서울경제</t>
+        </is>
+      </c>
+      <c r="F9" s="33" t="inlineStr">
+        <is>
+          <t>교차확인</t>
+        </is>
+      </c>
+      <c r="G9" s="33" t="inlineStr">
+        <is>
+          <t>클러스터 B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>연금·ISA</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>연금계좌 연간 순입금 중 11~12월</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>약 30%</t>
+        </is>
+      </c>
+      <c r="D10" s="33" t="inlineStr">
+        <is>
+          <t>KB증권 2023~24</t>
+        </is>
+      </c>
+      <c r="E10" s="33" t="inlineStr">
+        <is>
+          <t>국민일보, 한국경제</t>
+        </is>
+      </c>
+      <c r="F10" s="33" t="inlineStr">
+        <is>
+          <t>교차확인</t>
+        </is>
+      </c>
+      <c r="G10" s="33" t="inlineStr">
+        <is>
+          <t>연금 글 3주차로 앞당김</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>연금·ISA</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>ISA 잔액 1만원 이하 계좌</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>472만 (48.5%)</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E11" s="33" t="inlineStr">
+        <is>
+          <t>머니투데이</t>
+        </is>
+      </c>
+      <c r="F11" s="33" t="inlineStr">
+        <is>
+          <t>교차확인</t>
+        </is>
+      </c>
+      <c r="G11" s="33" t="inlineStr">
+        <is>
+          <t>잠자는 ISA 글</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>연금·ISA</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>세제개편안 직후 ISA 해지</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>전년 동기 약 3배</t>
+        </is>
+      </c>
+      <c r="D12" s="33" t="inlineStr">
+        <is>
+          <t>2026-08-03~07</t>
+        </is>
+      </c>
+      <c r="E12" s="33" t="inlineStr">
+        <is>
+          <t>이데일리</t>
+        </is>
+      </c>
+      <c r="F12" s="33" t="inlineStr">
+        <is>
+          <t>교차확인</t>
+        </is>
+      </c>
+      <c r="G12" s="33" t="inlineStr">
+        <is>
+          <t>ISA 철회 글 최우선</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="33" t="inlineStr">
+        <is>
+          <t>검색</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>검색 점유율 (인터넷트렌드)</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>네이버 64.3 / 구글 28.4 / 다음 2.9%</t>
+        </is>
+      </c>
+      <c r="D13" s="33" t="inlineStr">
+        <is>
+          <t>2026 상반기</t>
+        </is>
+      </c>
+      <c r="E13" s="33" t="inlineStr">
+        <is>
+          <t>디지털데일리, 아시아경제</t>
+        </is>
+      </c>
+      <c r="F13" s="33" t="inlineStr">
+        <is>
+          <t>교차확인</t>
+        </is>
+      </c>
+      <c r="G13" s="33" t="inlineStr">
+        <is>
+          <t>네이버 70 : 티스토리 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="33" t="inlineStr">
+        <is>
+          <t>검색</t>
+        </is>
+      </c>
+      <c r="B14" s="33" t="inlineStr">
+        <is>
+          <t>검색 점유율 (StatCounter)</t>
+        </is>
+      </c>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>구글 46.8 / 네이버 44.0%</t>
+        </is>
+      </c>
+      <c r="D14" s="33" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="E14" s="33" t="inlineStr">
+        <is>
+          <t>한국데이터경제신문</t>
+        </is>
+      </c>
+      <c r="F14" s="33" t="inlineStr">
+        <is>
+          <t>단일출처</t>
+        </is>
+      </c>
+      <c r="G14" s="33" t="inlineStr">
+        <is>
+          <t>측정 방식 차이 주의</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>검색</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>AI 브리핑 적용 비율</t>
+        </is>
+      </c>
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>20% → 목표 40%</t>
+        </is>
+      </c>
+      <c r="D15" s="33" t="inlineStr">
+        <is>
+          <t>2025년 말 → 2026년 말</t>
+        </is>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
+        <is>
+          <t>머니투데이, 서울경제TV</t>
+        </is>
+      </c>
+      <c r="F15" s="33" t="inlineStr">
+        <is>
+          <t>교차확인</t>
+        </is>
+      </c>
+      <c r="G15" s="33" t="inlineStr">
+        <is>
+          <t>인용 수를 핵심 KPI로</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="33" t="inlineStr">
+        <is>
+          <t>검색</t>
+        </is>
+      </c>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>AI 브리핑 인용 중 네이버 자체 콘텐츠</t>
+        </is>
+      </c>
+      <c r="C16" s="33" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E16" s="33" t="inlineStr">
+        <is>
+          <t>나스미디어, 비즈워치</t>
+        </is>
+      </c>
+      <c r="F16" s="33" t="inlineStr">
+        <is>
+          <t>교차확인</t>
+        </is>
+      </c>
+      <c r="G16" s="33" t="inlineStr">
+        <is>
+          <t>네이버 블로그 유리</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="33" t="inlineStr">
+        <is>
+          <t>검색</t>
+        </is>
+      </c>
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>네이버 메이트</t>
+        </is>
+      </c>
+      <c r="C17" s="33" t="inlineStr">
+        <is>
+          <t>월 약 3,000명, 월 30만원~</t>
+        </is>
+      </c>
+      <c r="D17" s="33" t="inlineStr">
+        <is>
+          <t>2026-06~</t>
+        </is>
+      </c>
+      <c r="E17" s="33" t="inlineStr">
+        <is>
+          <t>네이버 보도자료</t>
+        </is>
+      </c>
+      <c r="F17" s="33" t="inlineStr">
+        <is>
+          <t>교차확인</t>
+        </is>
+      </c>
+      <c r="G17" s="33" t="inlineStr">
+        <is>
+          <t>중기 목표</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="33" t="inlineStr">
+        <is>
+          <t>검색</t>
+        </is>
+      </c>
+      <c r="B18" s="33" t="inlineStr">
+        <is>
+          <t>구글 AI 요약 시 1위 CTR 변화</t>
+        </is>
+      </c>
+      <c r="C18" s="33" t="inlineStr">
+        <is>
+          <t>-58%</t>
+        </is>
+      </c>
+      <c r="D18" s="33" t="inlineStr">
+        <is>
+          <t>2025-12 데이터</t>
+        </is>
+      </c>
+      <c r="E18" s="33" t="inlineStr">
+        <is>
+          <t>Ahrefs</t>
+        </is>
+      </c>
+      <c r="F18" s="33" t="inlineStr">
+        <is>
+          <t>교차확인</t>
+        </is>
+      </c>
+      <c r="G18" s="33" t="inlineStr">
+        <is>
+          <t>구글 CTR 목표 하향</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="33" t="inlineStr">
+        <is>
+          <t>검색</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="inlineStr">
+        <is>
+          <t>AI 요약 인용 사이트 CTR</t>
+        </is>
+      </c>
+      <c r="C19" s="33" t="inlineStr">
+        <is>
+          <t>+35% (비인용 대비)</t>
+        </is>
+      </c>
+      <c r="D19" s="33" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="E19" s="33" t="inlineStr">
+        <is>
+          <t>Seer</t>
+        </is>
+      </c>
+      <c r="F19" s="33" t="inlineStr">
+        <is>
+          <t>교차확인</t>
+        </is>
+      </c>
+      <c r="G19" s="33" t="inlineStr">
+        <is>
+          <t>인용되는 구조로 쓰기</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="33" t="inlineStr">
+        <is>
+          <t>플랫폼</t>
+        </is>
+      </c>
+      <c r="B20" s="33" t="inlineStr">
+        <is>
+          <t>티스토리 운영사</t>
+        </is>
+      </c>
+      <c r="C20" s="33" t="inlineStr">
+        <is>
+          <t>업스테이지 인수 완료</t>
+        </is>
+      </c>
+      <c r="D20" s="33" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E20" s="33" t="inlineStr">
+        <is>
+          <t>파이낸셜뉴스, 딜사이트</t>
+        </is>
+      </c>
+      <c r="F20" s="33" t="inlineStr">
+        <is>
+          <t>교차확인</t>
+        </is>
+      </c>
+      <c r="G20" s="33" t="inlineStr">
+        <is>
+          <t>백업·도메인 리스크 관리</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>벤치마크</t>
+        </is>
+      </c>
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>신규 페이지 1년 내 구글 Top10</t>
+        </is>
+      </c>
+      <c r="C21" s="33" t="inlineStr">
+        <is>
+          <t>1.74%</t>
+        </is>
+      </c>
+      <c r="D21" s="33" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E21" s="33" t="inlineStr">
+        <is>
+          <t>Ahrefs</t>
+        </is>
+      </c>
+      <c r="F21" s="33" t="inlineStr">
+        <is>
+          <t>교차확인</t>
+        </is>
+      </c>
+      <c r="G21" s="33" t="inlineStr">
+        <is>
+          <t>티스토리 목표 하향</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="33" t="inlineStr">
+        <is>
+          <t>벤치마크</t>
+        </is>
+      </c>
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>2,000단어+ 작성자 강한 성과 비율</t>
+        </is>
+      </c>
+      <c r="C22" s="33" t="inlineStr">
+        <is>
+          <t>39% (전체 21%)</t>
+        </is>
+      </c>
+      <c r="D22" s="33" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E22" s="33" t="inlineStr">
+        <is>
+          <t>Orbit Media</t>
+        </is>
+      </c>
+      <c r="F22" s="33" t="inlineStr">
+        <is>
+          <t>교차확인</t>
+        </is>
+      </c>
+      <c r="G22" s="33" t="inlineStr">
+        <is>
+          <t>발행량↓, 깊이↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="33" t="inlineStr">
+        <is>
+          <t>벤치마크</t>
+        </is>
+      </c>
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>옛 글 최적화 효과</t>
+        </is>
+      </c>
+      <c r="C23" s="33" t="inlineStr">
+        <is>
+          <t>검색 조회수 +106%</t>
+        </is>
+      </c>
+      <c r="D23" s="33" t="inlineStr">
+        <is>
+          <t>2015년경</t>
+        </is>
+      </c>
+      <c r="E23" s="33" t="inlineStr">
+        <is>
+          <t>HubSpot</t>
+        </is>
+      </c>
+      <c r="F23" s="33" t="inlineStr">
+        <is>
+          <t>교차확인(구연구)</t>
+        </is>
+      </c>
+      <c r="G23" s="33" t="inlineStr">
+        <is>
+          <t>매주 업데이트 1편</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="33" t="inlineStr">
+        <is>
+          <t>일정</t>
+        </is>
+      </c>
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>금통위</t>
+        </is>
+      </c>
+      <c r="C24" s="33" t="inlineStr">
+        <is>
+          <t>10/22, 11/26 (12월 없음)</t>
+        </is>
+      </c>
+      <c r="D24" s="33" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E24" s="33" t="inlineStr">
+        <is>
+          <t>한국은행</t>
+        </is>
+      </c>
+      <c r="F24" s="33" t="inlineStr">
+        <is>
+          <t>교차확인</t>
+        </is>
+      </c>
+      <c r="G24" s="33" t="inlineStr">
+        <is>
+          <t>캘린더 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="33" t="inlineStr">
+        <is>
+          <t>일정</t>
+        </is>
+      </c>
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>세법 처리 법정기한</t>
+        </is>
+      </c>
+      <c r="C25" s="33" t="inlineStr">
+        <is>
+          <t>12/2</t>
+        </is>
+      </c>
+      <c r="D25" s="33" t="inlineStr">
+        <is>
+          <t>매년</t>
+        </is>
+      </c>
+      <c r="E25" s="33" t="inlineStr">
+        <is>
+          <t>국회예산정책처</t>
+        </is>
+      </c>
+      <c r="F25" s="33" t="inlineStr">
+        <is>
+          <t>교차확인</t>
+        </is>
+      </c>
+      <c r="G25" s="33" t="inlineStr">
+        <is>
+          <t>9주차 속보</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="33" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="B26" s="33" t="inlineStr">
+        <is>
+          <t>키워드별 월간 검색량</t>
+        </is>
+      </c>
+      <c r="C26" s="33" t="inlineStr">
+        <is>
+          <t>확보 못 함</t>
+        </is>
+      </c>
+      <c r="D26" s="33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E26" s="33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F26" s="33" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="G26" s="33" t="inlineStr">
+        <is>
+          <t>키워드백로그에 직접 입력</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>